--- a/XBRL-template-MFRS/12-Notes-ListOfNotes.xlsx
+++ b/XBRL-template-MFRS/12-Notes-ListOfNotes.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,15 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,6 +99,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,12 +480,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>

--- a/XBRL-template-MFRS/12-Notes-ListOfNotes.xlsx
+++ b/XBRL-template-MFRS/12-Notes-ListOfNotes.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +50,31 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +86,14 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -84,11 +115,21 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +146,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,1274 +530,1419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="6" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Notes - List of notes</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Disclosure of accrued expenses and other liabilities</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Disclosure of acquisitions and disposals</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Disclosure of allowance for credit losses</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="12" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Disclosure of amendments to MFRS and pronouncements issued by MASB</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="12" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Disclosure of auditors' remuneration</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="12" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Disclosure of authorisation of financial statements</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Disclosure of basis of preparation of financial statements</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Disclosure of biological assets</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Disclosure of bonds</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Disclosure of borrowings</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Disclosure of business combinations</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Disclosure of capital and other commitments</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Disclosure of capital management</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Disclosure of cash and bank balances at central banks</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Disclosure of cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Disclosure of cash flow reconciliation</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Disclosure of cash held under housing development accounts</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Disclosure of changes in accounting policies, accounting estimates and errors</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Disclosure of claims and benefits paid</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Disclosure of collateral</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Disclosure of commodity price risk</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Disclosure of comparative figures</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Disclosure of construction contracts</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Disclosure of contingent assets and contingent liabilities</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Disclosure of corporate proposals</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Disclosure of cost of sales</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Disclosure of credit risk</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Disclosure of critical accounting estimates and judgements</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Disclosure of deferred income</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Disclosure of deferred tax assets/(liabilities)</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Disclosure of deposits from banks</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Disclosure of deposits with financial institutions</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Disclosure of depreciation and amortisation expense</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Disclosure of derivative financial assets/liabilities</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Disclosure of development expenditures</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Disclosure of discontinued operations</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Disclosure of disposal of subsidiaries</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Disclosure of dividends</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Disclosure of earnings (loss) per share</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Disclosure of effect of changes in foreign exchange rates</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Disclosure of employee benefits expense</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="12" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Disclosure of employment termination benefits</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="12" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Disclosure of entity's operating segments</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="12" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Disclosure of equity price risk</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="12" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Disclosure of events after reporting period</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Disclosure of fair value information</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="12" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Disclosure of fair value measurement</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Disclosure of fair value of financial instruments</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="12" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Disclosure of fee and commission income (expense)</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="12" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Disclosure of fees for non-audit services provided by the Company's auditor and its member firms</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="12" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Disclosure of finance costs</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="12" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Disclosure of finance income</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="12" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial assets at fair value through other comprehensive income</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="12" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial guarantees</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="12" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial instrument measured at amortised cost</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="12" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial instruments</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="12" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial instruments at fair value through profit or loss</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="12" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial instruments held for trading</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="12" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Disclosure of financial liabilities measured at amortised cost</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="12" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Disclosure of first-time adoption</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>Disclosure of foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="12" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Disclosure of general information about financial statements</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="12" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Disclosure of going concern</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="12" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Disclosure of grants and contributions</t>
         </is>
       </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="12" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Disclosure of gross profit</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="12" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>Disclosure of held to maturity investment</t>
         </is>
       </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="12" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Disclosure of holding companies</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="12" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>Disclosure of income tax expense</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="12" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>Disclosure of intangible assets and goodwill</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="12" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>Disclosure of interest in joint operation</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="12" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>Disclosure of interests in unconsolidated structured entities</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="12" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Disclosure of interest rate risk</t>
         </is>
       </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="12" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Disclosure of inventories</t>
         </is>
       </c>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="12" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Disclosure of investment property</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="12" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>Disclosure of investments in associates</t>
         </is>
       </c>
-      <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="12" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>Disclosure of investments in joint ventures</t>
         </is>
       </c>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="4" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="12" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>Disclosure of investments in subsidiary companies</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="12" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Disclosure of irredeemable convertible unsecured loan stocks</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="12" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Disclosure of islamic financing facilities</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="12" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Disclosure of issued capital</t>
         </is>
       </c>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="12" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Disclosure of key management personnel compensation</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="12" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>Disclosure of land held for development</t>
         </is>
       </c>
-      <c r="B85" s="4" t="n"/>
-      <c r="C85" s="4" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="12" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>Disclosure of lease prepayments</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="12" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Disclosure of leases</t>
         </is>
       </c>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="12" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>Disclosure of liquidity risk</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="4" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="12" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Disclosure of list of subsidiaries, joint ventures and associates</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="12" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Disclosure of loans and advances to banks</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="12" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Disclosure of loans and receivables</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="12" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Disclosure of long term payables</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="12" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>Disclosure of long term receivables</t>
         </is>
       </c>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="12" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Disclosure of maturity analysis under liquidity risk</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="12" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>Disclosure of net asset value attributable to unit-holders</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="12" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>Disclosure of net gains and losses arising from financial instruments</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="12" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Disclosure of non-controlling interests</t>
         </is>
       </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="12" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Disclosure of non-current assets or disposal groups classified as held for sale and discontinued operations</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="12" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>Disclosure of non-derivative financial instruments</t>
         </is>
       </c>
-      <c r="B99" s="4" t="n"/>
-      <c r="C99" s="4" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="12" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>Disclosure of non-executive director's fees</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="12" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other current assets</t>
         </is>
       </c>
-      <c r="B101" s="4" t="n"/>
-      <c r="C101" s="4" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="10" t="n"/>
+      <c r="D101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other current liabilities</t>
         </is>
       </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="10" t="n"/>
+      <c r="D102" s="12" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other financial risk management</t>
         </is>
       </c>
-      <c r="B103" s="4" t="n"/>
-      <c r="C103" s="4" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="12" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other gains and losses</t>
         </is>
       </c>
-      <c r="B104" s="4" t="n"/>
-      <c r="C104" s="4" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="B104" s="10" t="n"/>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="12" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other guarantees</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n"/>
-      <c r="C105" s="4" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="12" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other income</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="12" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other investments</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="12" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other long term employment benefits</t>
         </is>
       </c>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="12" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other market risk</t>
         </is>
       </c>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="12" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other non-current assets</t>
         </is>
       </c>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="4" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other non-current liabilities</t>
         </is>
       </c>
-      <c r="B111" s="4" t="n"/>
-      <c r="C111" s="4" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="12" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other notes to accounts</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="12" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other operating expenses</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="12" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other operating income</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="12" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other provisions</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="12" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>Disclosure of other reserves</t>
         </is>
       </c>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="12" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>Disclosure of perpetual sukuk</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n"/>
-      <c r="C117" s="4" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="10" t="n"/>
+      <c r="D117" s="12" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>Disclosure of post employment benefit obligation</t>
         </is>
       </c>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="12" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>Disclosure of price risk</t>
         </is>
       </c>
-      <c r="B119" s="4" t="n"/>
-      <c r="C119" s="4" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="12" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>Disclosure of prior year adjustments</t>
         </is>
       </c>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="B120" s="10" t="n"/>
+      <c r="C120" s="10" t="n"/>
+      <c r="D120" s="12" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>Disclosure of profit after tax</t>
         </is>
       </c>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="12" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>Disclosure of profit before tax</t>
         </is>
       </c>
-      <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="B122" s="10" t="n"/>
+      <c r="C122" s="10" t="n"/>
+      <c r="D122" s="12" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>Disclosure of progress billings and others</t>
         </is>
       </c>
-      <c r="B123" s="4" t="n"/>
-      <c r="C123" s="4" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="12" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>Disclosure of property development costs</t>
         </is>
       </c>
-      <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="12" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>Disclosure of property, plant and equipment</t>
         </is>
       </c>
-      <c r="B125" s="4" t="n"/>
-      <c r="C125" s="4" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="B125" s="10" t="n"/>
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="12" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>Disclosure of research and development expense</t>
         </is>
       </c>
-      <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="10" t="n"/>
+      <c r="D126" s="12" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>Disclosure of revenue from contract customers</t>
         </is>
       </c>
-      <c r="B127" s="4" t="n"/>
-      <c r="C127" s="4" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="B127" s="10" t="n"/>
+      <c r="C127" s="10" t="n"/>
+      <c r="D127" s="12" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>Disclosure of service concession arrangements</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="10" t="n"/>
+      <c r="D128" s="12" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>Disclosure of share capital</t>
         </is>
       </c>
-      <c r="B129" s="4" t="n"/>
-      <c r="C129" s="4" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="12" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>Disclosure of share-based payment arrangements</t>
         </is>
       </c>
-      <c r="B130" s="4" t="n"/>
-      <c r="C130" s="4" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="B130" s="10" t="n"/>
+      <c r="C130" s="10" t="n"/>
+      <c r="D130" s="12" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>Disclosure of short term investments</t>
         </is>
       </c>
-      <c r="B131" s="4" t="n"/>
-      <c r="C131" s="4" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="12" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>Disclosure of significant events during the financial year</t>
         </is>
       </c>
-      <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B132" s="10" t="n"/>
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="12" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>Disclosure of statement of compliance</t>
         </is>
       </c>
-      <c r="B133" s="4" t="n"/>
-      <c r="C133" s="4" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="B133" s="10" t="n"/>
+      <c r="C133" s="10" t="n"/>
+      <c r="D133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>Disclosure of supplementary financial information on the breakdown of realised and unrealised profits or losses</t>
         </is>
       </c>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="12" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>Disclosure of tax receivables and payables</t>
         </is>
       </c>
-      <c r="B135" s="4" t="n"/>
-      <c r="C135" s="4" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="B135" s="10" t="n"/>
+      <c r="C135" s="10" t="n"/>
+      <c r="D135" s="12" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>Disclosure of tax supplementary information</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B136" s="10" t="n"/>
+      <c r="C136" s="10" t="n"/>
+      <c r="D136" s="12" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>Disclosure of the new or revised financial reporting standards not yet effective</t>
         </is>
       </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="B137" s="10" t="n"/>
+      <c r="C137" s="10" t="n"/>
+      <c r="D137" s="12" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>Disclosure of trade and other inventories</t>
         </is>
       </c>
-      <c r="B138" s="4" t="n"/>
-      <c r="C138" s="4" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="12" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>Disclosure of trade and other payables</t>
         </is>
       </c>
-      <c r="B139" s="4" t="n"/>
-      <c r="C139" s="4" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="10" t="n"/>
+      <c r="D139" s="12" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>Disclosure of trade and other receivables</t>
         </is>
       </c>
-      <c r="B140" s="4" t="n"/>
-      <c r="C140" s="4" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="12" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>Disclosure of treasury shares</t>
         </is>
       </c>
-      <c r="B141" s="4" t="n"/>
-      <c r="C141" s="4" t="n"/>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
